--- a/files/港岛-筲箕湾-远晴.xlsx
+++ b/files/港岛-筲箕湾-远晴.xlsx
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-10-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-18</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-10-07</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-12-09</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-10-05</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-12-17</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-04</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-03</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-25</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-10-26</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-24</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-24</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-04</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-24</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-09-04</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5447,7 +5447,7 @@
           <t>A | 434呎 (1房)
 $782万
 $18,028/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -5455,7 +5455,7 @@
           <t>B | 271呎 (1房)
 $555万
 $20,469/呎
-(已售)</t>
+(14年-10月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -5463,7 +5463,7 @@
           <t>C | 276呎 (1房)
 $568万
 $20,598/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -5486,7 +5486,7 @@
           <t>A | 434呎 (1房)
 $780万
 $17,984/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -5494,7 +5494,7 @@
           <t>B | 271呎 (1房)
 $553万
 $20,417/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -5502,7 +5502,7 @@
           <t>C | 276呎 (1房)
 $567万
 $20,543/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -5525,7 +5525,7 @@
           <t>A | 434呎 (1房)
 $746万
 $17,189/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -5533,7 +5533,7 @@
           <t>B | 271呎 (1房)
 $542万
 $20,011/呎
-(已售)</t>
+(14年-10月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -5541,7 +5541,7 @@
           <t>C | 276呎 (1房)
 $556万
 $20,141/呎
-(已售)</t>
+(14年-10月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -5564,7 +5564,7 @@
           <t>A | 434呎 (1房)
 $742万
 $17,099/呎
-(已售)</t>
+(14年-12月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -5572,7 +5572,7 @@
           <t>B | 271呎 (1房)
 $537万
 $19,812/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -5580,7 +5580,7 @@
           <t>C | 275呎 (1房)
 $550万
 $20,011/呎
-(已售)</t>
+(14年-10月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -5611,7 +5611,7 @@
           <t>B | 274呎 (1房)
 $532万
 $19,401/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -5619,7 +5619,7 @@
           <t>C | 276呎 (1房)
 $545万
 $19,739/呎
-(已售)</t>
+(14年-10月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -5642,7 +5642,7 @@
           <t>A | 431呎 (1房)
 $723万
 $16,773/呎
-(已售)</t>
+(14年-12月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -5650,7 +5650,7 @@
           <t>B | 274呎 (1房)
 $529万
 $19,321/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -5658,7 +5658,7 @@
           <t>C | 276呎 (1房)
 $537万
 $19,446/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -5681,7 +5681,7 @@
           <t>A | 431呎 (1房)
 $716万
 $16,608/呎
-(已售)</t>
+(14年-10月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -5697,7 +5697,7 @@
           <t>C | 275呎 (1房)
 $531万
 $19,320/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -5720,7 +5720,7 @@
           <t>A | 431呎 (1房)
 $709万
 $16,443/呎
-(已售)</t>
+(14年-10月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -5728,7 +5728,7 @@
           <t>B | 274呎 (1房)
 $519万
 $18,938/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -5736,7 +5736,7 @@
           <t>C | 276呎 (1房)
 $526万
 $19,062/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -5759,7 +5759,7 @@
           <t>A | 431呎 (1房)
 $701万
 $16,271/呎
-(已售)</t>
+(14年-10月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -5767,7 +5767,7 @@
           <t>B | 274呎 (1房)
 $514万
 $18,752/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5775,7 +5775,7 @@
           <t>C | 276呎 (1房)
 $521万
 $18,870/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -5798,7 +5798,7 @@
           <t>A | 431呎 (1房)
 $674万
 $15,643/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -5806,7 +5806,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,832/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5837,7 +5837,7 @@
           <t>A | 431呎 (1房)
 $674万
 $15,643/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -5845,7 +5845,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,832/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5876,7 +5876,7 @@
           <t>A | 431呎 (1房)
 $667万
 $15,485/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5884,7 +5884,7 @@
           <t>B | 274呎 (1房)
 $484万
 $17,653/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5892,7 +5892,7 @@
           <t>C | 275呎 (1房)
 $486万
 $17,655/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -5915,7 +5915,7 @@
           <t>A | 431呎 (1房)
 $650万
 $15,072/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5954,7 +5954,7 @@
           <t>A | 431呎 (1房)
 $661万
 $15,334/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -5962,7 +5962,7 @@
           <t>B | 274呎 (1房)
 $479万
 $17,478/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -5970,7 +5970,7 @@
           <t>C | 276呎 (1房)
 $481万
 $17,417/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -5993,7 +5993,7 @@
           <t>A | 431呎 (1房)
 $658万
 $15,255/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -6032,7 +6032,7 @@
           <t>A | 431呎 (1房)
 $654万
 $15,179/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -6040,7 +6040,7 @@
           <t>B | 274呎 (1房)
 $474万
 $17,307/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -6048,7 +6048,7 @@
           <t>C | 276呎 (1房)
 $476万
 $17,243/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -6071,7 +6071,7 @@
           <t>A | 431呎 (1房)
 $651万
 $15,104/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -6079,7 +6079,7 @@
           <t>B | 274呎 (1房)
 $479万
 $17,493/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -6087,7 +6087,7 @@
           <t>C | 276呎 (1房)
 $486万
 $17,605/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -6110,7 +6110,7 @@
           <t>A | 431呎 (1房)
 $648万
 $15,030/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -6118,7 +6118,7 @@
           <t>B | 274呎 (1房)
 $477万
 $17,409/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -6126,7 +6126,7 @@
           <t>C | 276呎 (1房)
 $484万
 $17,518/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -6149,7 +6149,7 @@
           <t>A | 431呎 (1房)
 $648万
 $15,030/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -6157,7 +6157,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,847/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -6165,7 +6165,7 @@
           <t>C | 276呎 (1房)
 $496万
 $17,964/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -6196,7 +6196,7 @@
           <t>B | 274呎 (1房)
 $472万
 $17,234/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -6204,7 +6204,7 @@
           <t>C | 276呎 (1房)
 $479万
 $17,344/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -6227,7 +6227,7 @@
           <t>A | 431呎 (1房)
 $629万
 $14,587/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -6243,7 +6243,7 @@
           <t>C | 276呎 (1房)
 $462万
 $16,757/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -6266,7 +6266,7 @@
           <t>A | 431呎 (1房)
 $616万
 $14,302/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -6274,7 +6274,7 @@
           <t>B | 274呎 (1房)
 $454万
 $16,562/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -6282,7 +6282,7 @@
           <t>C | 276呎 (1房)
 $435万
 $15,775/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -6313,7 +6313,7 @@
           <t>B | 253呎 (1房)
 $500万
 $19,751/呎
-(已售)</t>
+(14年-09月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -6329,7 +6329,7 @@
           <t>D | 490呎 (2房)
 $812万
 $16,567/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-筲箕湾-远晴.xlsx
+++ b/files/港岛-筲箕湾-远晴.xlsx
@@ -205,61 +205,61 @@
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -645,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-筲箕湾-远晴.xlsx
+++ b/files/港岛-筲箕湾-远晴.xlsx
@@ -205,61 +205,61 @@
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -645,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
